--- a/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3870" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3869" uniqueCount="333">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T08:45:11+00:00</t>
+    <t>2025-07-08T14:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -989,6 +989,9 @@
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-schedule-unavailability-reason</t>
   </si>
   <si>
     <t>Extension.extension:created</t>
@@ -1376,7 +1379,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.9921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -12361,13 +12364,11 @@
         <v>77</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>77</v>
+        <v>318</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>77</v>
@@ -12405,13 +12406,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>77</v>
@@ -12436,10 +12437,10 @@
         <v>92</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12510,7 +12511,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>101</v>
@@ -12613,7 +12614,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>103</v>
@@ -12716,7 +12717,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>105</v>
@@ -12759,7 +12760,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>77</v>
@@ -12821,7 +12822,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>113</v>
@@ -12924,13 +12925,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>77</v>
@@ -13029,7 +13030,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>101</v>
@@ -13132,7 +13133,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>103</v>
@@ -13235,7 +13236,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>105</v>
@@ -13278,7 +13279,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>77</v>
@@ -13340,7 +13341,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>113</v>

--- a/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
+++ b/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-schedule-availability-time.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T14:52:18+00:00</t>
+    <t>2025-07-10T12:55:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
